--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1263,7 +1263,7 @@
         <v>129627569</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129627570</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129627554</v>
       </c>
       <c r="B12" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129627556</v>
       </c>
       <c r="B18" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129627549</v>
       </c>
       <c r="B19" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>129627560</v>
       </c>
       <c r="B20" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>129627573</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83031</v>
+        <v>83036</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>129643507</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>129643527</v>
       </c>
       <c r="B27" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>129643519</v>
       </c>
       <c r="B28" t="n">
-        <v>97038</v>
+        <v>97050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>129643536</v>
       </c>
       <c r="B29" t="n">
-        <v>83022</v>
+        <v>83027</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>97002</v>
+        <v>98768</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R30" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>98756</v>
+        <v>97014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R31" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,49 +3824,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129643528</v>
+        <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>97014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361397</v>
+        <v>361389</v>
       </c>
       <c r="R32" t="n">
-        <v>6599608</v>
+        <v>6599624</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,7 +3913,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3936,45 +3931,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129643499</v>
+        <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>97002</v>
+        <v>98768</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>361389</v>
+        <v>361397</v>
       </c>
       <c r="R33" t="n">
-        <v>6599624</v>
+        <v>6599608</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4006,7 +4005,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4016,7 +4015,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4025,6 +4024,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>129643495</v>
       </c>
       <c r="B35" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>129643538</v>
       </c>
       <c r="B36" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4364,32 +4364,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643494</v>
+        <v>129643548</v>
       </c>
       <c r="B37" t="n">
-        <v>97002</v>
+        <v>92869</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361360</v>
+        <v>361330</v>
       </c>
       <c r="R37" t="n">
-        <v>6599480</v>
+        <v>6599547</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4471,49 +4471,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643524</v>
+        <v>129643494</v>
       </c>
       <c r="B38" t="n">
-        <v>98756</v>
+        <v>97014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361109</v>
+        <v>361360</v>
       </c>
       <c r="R38" t="n">
-        <v>6599524</v>
+        <v>6599480</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4545,7 +4541,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4555,7 +4551,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,7 +4560,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4583,45 +4578,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643548</v>
+        <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>92863</v>
+        <v>98768</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361330</v>
+        <v>361109</v>
       </c>
       <c r="R39" t="n">
-        <v>6599547</v>
+        <v>6599524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,7 +4652,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4663,7 +4662,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,6 +4671,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,45 +4690,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R40" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4764,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,6 +4783,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4797,49 +4802,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>91587</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R41" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>129643522</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643501</v>
+        <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5056,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361403</v>
+        <v>361373</v>
       </c>
       <c r="R43" t="n">
-        <v>6599594</v>
+        <v>6599657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5128,10 +5128,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643497</v>
+        <v>129643501</v>
       </c>
       <c r="B44" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5163,10 +5163,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361373</v>
+        <v>361403</v>
       </c>
       <c r="R44" t="n">
-        <v>6599657</v>
+        <v>6599594</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91545</v>
+        <v>91551</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129643531</v>
+        <v>129643521</v>
       </c>
       <c r="B46" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>361166</v>
+        <v>361383</v>
       </c>
       <c r="R46" t="n">
-        <v>6599518</v>
+        <v>6599668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5454,10 +5454,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129643521</v>
+        <v>129643531</v>
       </c>
       <c r="B47" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>361383</v>
+        <v>361166</v>
       </c>
       <c r="R47" t="n">
-        <v>6599668</v>
+        <v>6599518</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5569,7 +5569,7 @@
         <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5894,6 +5894,331 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129752896</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bråne Glaskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>361227</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6599452</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129752901</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bråne Glaskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>361227</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6599452</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Grova hack- och fläkmärken</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129752902</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Bråne Glaskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>361227</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6599452</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>129627569</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129627570</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627554</v>
+        <v>129627568</v>
       </c>
       <c r="B12" t="n">
-        <v>56925</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361293</v>
+        <v>361409</v>
       </c>
       <c r="R12" t="n">
-        <v>6599542</v>
+        <v>6599609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627568</v>
+        <v>129627554</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>56926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361409</v>
+        <v>361293</v>
       </c>
       <c r="R13" t="n">
-        <v>6599609</v>
+        <v>6599542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>57895</v>
+        <v>91552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R18" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B19" t="n">
-        <v>91551</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R19" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2534,7 +2534,7 @@
         <v>129627560</v>
       </c>
       <c r="B20" t="n">
-        <v>97050</v>
+        <v>97051</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>129627573</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83036</v>
+        <v>83037</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>129643507</v>
       </c>
       <c r="B25" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,54 +3167,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>98769</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R26" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,7 +3241,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3256,7 +3251,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,49 +3279,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643527</v>
+        <v>129643517</v>
       </c>
       <c r="B27" t="n">
-        <v>98768</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361330</v>
+        <v>361186</v>
       </c>
       <c r="R27" t="n">
-        <v>6599531</v>
+        <v>6599443</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B28" t="n">
-        <v>97050</v>
+        <v>83028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R28" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B29" t="n">
-        <v>83027</v>
+        <v>97051</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R29" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3613,7 +3613,7 @@
         <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>129643495</v>
       </c>
       <c r="B35" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>129643538</v>
       </c>
       <c r="B36" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>129643548</v>
       </c>
       <c r="B37" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>129643494</v>
       </c>
       <c r="B38" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4690,49 +4690,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R40" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,7 +4760,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4783,7 +4779,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4802,45 +4797,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B41" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R41" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4882,7 +4881,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4891,6 +4890,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,49 +4909,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>97015</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R42" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4993,7 +4989,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +4998,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5024,7 +5019,7 @@
         <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,45 +5123,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>97014</v>
+        <v>98769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R44" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5197,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5207,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,6 +5216,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129643521</v>
+        <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>361383</v>
+        <v>361166</v>
       </c>
       <c r="R46" t="n">
-        <v>6599668</v>
+        <v>6599518</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5454,10 +5454,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129643531</v>
+        <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>361166</v>
+        <v>361383</v>
       </c>
       <c r="R47" t="n">
-        <v>6599518</v>
+        <v>6599668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5566,45 +5566,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B48" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R48" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,7 +5640,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,6 +5659,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5673,49 +5678,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R49" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5747,7 +5748,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5757,7 +5758,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5767,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>129752896</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129752901</v>
       </c>
       <c r="B52" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627568</v>
+        <v>129627554</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>56926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361409</v>
+        <v>361293</v>
       </c>
       <c r="R12" t="n">
-        <v>6599609</v>
+        <v>6599542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1847,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627554</v>
+        <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>56926</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361293</v>
+        <v>361409</v>
       </c>
       <c r="R13" t="n">
-        <v>6599542</v>
+        <v>6599609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B18" t="n">
-        <v>91552</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R18" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>91552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R19" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,32 +2531,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627560</v>
+        <v>129627573</v>
       </c>
       <c r="B20" t="n">
-        <v>97051</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361478</v>
+        <v>361160</v>
       </c>
       <c r="R20" t="n">
-        <v>6599641</v>
+        <v>6599438</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627573</v>
+        <v>129627560</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>97051</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361160</v>
+        <v>361478</v>
       </c>
       <c r="R21" t="n">
-        <v>6599438</v>
+        <v>6599641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>97015</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R30" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>97015</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R31" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,45 +3824,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129643499</v>
+        <v>129643528</v>
       </c>
       <c r="B32" t="n">
-        <v>97015</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361389</v>
+        <v>361397</v>
       </c>
       <c r="R32" t="n">
-        <v>6599624</v>
+        <v>6599608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3904,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,6 +3917,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3931,49 +3936,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129643528</v>
+        <v>129643499</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>97015</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>361397</v>
+        <v>361389</v>
       </c>
       <c r="R33" t="n">
-        <v>6599608</v>
+        <v>6599624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4005,7 +4006,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4015,7 +4016,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,7 +4025,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5566,49 +5566,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>98769</v>
+        <v>91588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R48" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5640,7 +5636,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5650,7 +5646,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5655,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5678,45 +5673,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>91588</v>
+        <v>98769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R49" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5747,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5758,7 +5757,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5767,6 +5766,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>129627569</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129627570</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>91557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R18" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B19" t="n">
-        <v>91552</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R19" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,32 +2531,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627573</v>
+        <v>129627560</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>97056</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361160</v>
+        <v>361478</v>
       </c>
       <c r="R20" t="n">
-        <v>6599438</v>
+        <v>6599641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627560</v>
+        <v>129627573</v>
       </c>
       <c r="B21" t="n">
-        <v>97051</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361478</v>
+        <v>361160</v>
       </c>
       <c r="R21" t="n">
-        <v>6599641</v>
+        <v>6599438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83037</v>
+        <v>83042</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>129643507</v>
       </c>
       <c r="B25" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>129643527</v>
       </c>
       <c r="B26" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>129643536</v>
       </c>
       <c r="B28" t="n">
-        <v>83028</v>
+        <v>83033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>129643519</v>
       </c>
       <c r="B29" t="n">
-        <v>97051</v>
+        <v>97056</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643528</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>129643499</v>
       </c>
       <c r="B33" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,32 +4150,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129643495</v>
+        <v>129643538</v>
       </c>
       <c r="B35" t="n">
-        <v>97015</v>
+        <v>90975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5685</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>361450</v>
+        <v>361240</v>
       </c>
       <c r="R35" t="n">
-        <v>6599606</v>
+        <v>6599499</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,32 +4257,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129643538</v>
+        <v>129643495</v>
       </c>
       <c r="B36" t="n">
-        <v>90970</v>
+        <v>97020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>361240</v>
+        <v>361450</v>
       </c>
       <c r="R36" t="n">
-        <v>6599499</v>
+        <v>6599606</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4364,32 +4364,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643548</v>
+        <v>129643494</v>
       </c>
       <c r="B37" t="n">
-        <v>92870</v>
+        <v>97020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361330</v>
+        <v>361360</v>
       </c>
       <c r="R37" t="n">
-        <v>6599547</v>
+        <v>6599480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4471,32 +4471,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643494</v>
+        <v>129643548</v>
       </c>
       <c r="B38" t="n">
-        <v>97015</v>
+        <v>92875</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361360</v>
+        <v>361330</v>
       </c>
       <c r="R38" t="n">
-        <v>6599480</v>
+        <v>6599547</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4581,7 +4581,7 @@
         <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>129643511</v>
       </c>
       <c r="B40" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         <v>129643525</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,45 +4909,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B42" t="n">
-        <v>97015</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R42" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4989,7 +4993,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,6 +5002,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5016,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643497</v>
+        <v>129643501</v>
       </c>
       <c r="B43" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5051,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361373</v>
+        <v>361403</v>
       </c>
       <c r="R43" t="n">
-        <v>6599657</v>
+        <v>6599594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5086,7 +5091,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5123,49 +5128,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643522</v>
+        <v>129643497</v>
       </c>
       <c r="B44" t="n">
-        <v>98769</v>
+        <v>97020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361185</v>
+        <v>361373</v>
       </c>
       <c r="R44" t="n">
-        <v>6599497</v>
+        <v>6599657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,7 +5198,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5207,7 +5208,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,7 +5217,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91552</v>
+        <v>91557</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -3060,45 +3060,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643507</v>
+        <v>129643527</v>
       </c>
       <c r="B25" t="n">
-        <v>91557</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361447</v>
+        <v>361330</v>
       </c>
       <c r="R25" t="n">
-        <v>6599629</v>
+        <v>6599531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,7 +3134,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3140,7 +3144,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,6 +3153,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3167,49 +3172,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643527</v>
+        <v>129643507</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>91557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361330</v>
+        <v>361447</v>
       </c>
       <c r="R26" t="n">
-        <v>6599531</v>
+        <v>6599629</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3241,7 +3242,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3251,7 +3252,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3260,7 +3261,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B28" t="n">
-        <v>83033</v>
+        <v>97056</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R28" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B29" t="n">
-        <v>97056</v>
+        <v>83033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R29" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3824,49 +3824,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129643528</v>
+        <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>97020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361397</v>
+        <v>361389</v>
       </c>
       <c r="R32" t="n">
-        <v>6599608</v>
+        <v>6599624</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,7 +3913,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3936,45 +3931,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129643499</v>
+        <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>361389</v>
+        <v>361397</v>
       </c>
       <c r="R33" t="n">
-        <v>6599624</v>
+        <v>6599608</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4006,7 +4005,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4016,7 +4015,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4025,6 +4024,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4690,45 +4690,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R40" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4764,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,6 +4783,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4797,49 +4802,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R41" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,49 +4909,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>97020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R42" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4993,7 +4989,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +4998,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5021,7 +5016,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643501</v>
+        <v>129643497</v>
       </c>
       <c r="B43" t="n">
         <v>97020</v>
@@ -5056,10 +5051,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361403</v>
+        <v>361373</v>
       </c>
       <c r="R43" t="n">
-        <v>6599594</v>
+        <v>6599657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,7 +5086,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5101,7 +5096,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5128,45 +5123,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643497</v>
+        <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361373</v>
+        <v>361185</v>
       </c>
       <c r="R44" t="n">
-        <v>6599657</v>
+        <v>6599497</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5197,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5207,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,6 +5216,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B18" t="n">
-        <v>91557</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R18" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>91557</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R19" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3060,49 +3060,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643527</v>
+        <v>129643517</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361330</v>
+        <v>361186</v>
       </c>
       <c r="R25" t="n">
-        <v>6599531</v>
+        <v>6599443</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3144,7 +3149,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3279,54 +3284,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R27" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R30" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>97020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R31" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4364,45 +4364,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643494</v>
+        <v>129643524</v>
       </c>
       <c r="B37" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361360</v>
+        <v>361109</v>
       </c>
       <c r="R37" t="n">
-        <v>6599480</v>
+        <v>6599524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4438,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4448,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4453,6 +4457,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4471,32 +4476,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643548</v>
+        <v>129643494</v>
       </c>
       <c r="B38" t="n">
-        <v>92875</v>
+        <v>97020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4506,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361330</v>
+        <v>361360</v>
       </c>
       <c r="R38" t="n">
-        <v>6599547</v>
+        <v>6599480</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,7 +4546,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,49 +4583,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643524</v>
+        <v>129643548</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>92875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361109</v>
+        <v>361330</v>
       </c>
       <c r="R39" t="n">
-        <v>6599524</v>
+        <v>6599547</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4652,7 +4653,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4662,7 +4663,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,7 +4672,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,49 +4690,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R40" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,7 +4760,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4783,7 +4779,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4802,45 +4797,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B41" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R41" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4882,7 +4881,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4891,6 +4890,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5566,45 +5566,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B48" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R48" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,7 +5640,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,6 +5659,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5673,49 +5678,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R49" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5747,7 +5748,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5757,7 +5758,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5767,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Torbjörn Westerberg, Göran Carlzon</t>
+          <t>Göran Carlzon, Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Torbjörn Westerberg, Göran Carlzon</t>
+          <t>Göran Carlzon, Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Torbjörn Westerberg, Göran Carlzon</t>
+          <t>Göran Carlzon, Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627554</v>
+        <v>129627568</v>
       </c>
       <c r="B12" t="n">
-        <v>56926</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361293</v>
+        <v>361409</v>
       </c>
       <c r="R12" t="n">
-        <v>6599542</v>
+        <v>6599609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627568</v>
+        <v>129627554</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>56926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361409</v>
+        <v>361293</v>
       </c>
       <c r="R13" t="n">
-        <v>6599609</v>
+        <v>6599542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>91557</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R18" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B19" t="n">
-        <v>91557</v>
+        <v>57896</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R19" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B28" t="n">
-        <v>97056</v>
+        <v>83033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R28" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B29" t="n">
-        <v>83033</v>
+        <v>97056</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R29" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>97020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R30" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>97020</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R31" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4150,32 +4150,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129643538</v>
+        <v>129643495</v>
       </c>
       <c r="B35" t="n">
-        <v>90975</v>
+        <v>97020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>361240</v>
+        <v>361450</v>
       </c>
       <c r="R35" t="n">
-        <v>6599499</v>
+        <v>6599606</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,32 +4257,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129643495</v>
+        <v>129643538</v>
       </c>
       <c r="B36" t="n">
-        <v>97020</v>
+        <v>90975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>5685</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>361450</v>
+        <v>361240</v>
       </c>
       <c r="R36" t="n">
-        <v>6599606</v>
+        <v>6599499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4364,49 +4364,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643524</v>
+        <v>129643548</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>92875</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361109</v>
+        <v>361330</v>
       </c>
       <c r="R37" t="n">
-        <v>6599524</v>
+        <v>6599547</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4448,7 +4444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4457,7 +4453,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4583,45 +4578,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643548</v>
+        <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>92875</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361330</v>
+        <v>361109</v>
       </c>
       <c r="R39" t="n">
-        <v>6599547</v>
+        <v>6599524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,7 +4652,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4663,7 +4662,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,6 +4671,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,45 +4690,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R40" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4764,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,6 +4783,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4797,49 +4802,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R41" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5566,49 +5566,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R48" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5640,7 +5636,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5650,7 +5646,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5655,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5678,45 +5673,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R49" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5747,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5758,7 +5757,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5767,6 +5766,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R7" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R8" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129627568</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         <v>129627560</v>
       </c>
       <c r="B20" t="n">
-        <v>97056</v>
+        <v>97060</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>129627573</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643517</v>
+        <v>129643507</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>91561</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,43 +3071,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361186</v>
+        <v>361447</v>
       </c>
       <c r="R25" t="n">
-        <v>6599443</v>
+        <v>6599629</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,7 +3130,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3149,7 +3140,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3158,7 +3149,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3177,10 +3167,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643507</v>
+        <v>129643517</v>
       </c>
       <c r="B26" t="n">
-        <v>91557</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3188,34 +3178,43 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361447</v>
+        <v>361186</v>
       </c>
       <c r="R26" t="n">
-        <v>6599629</v>
+        <v>6599443</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,7 +3246,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3257,7 +3256,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3266,6 +3265,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>129643527</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B28" t="n">
-        <v>83033</v>
+        <v>97060</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R28" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B29" t="n">
-        <v>97056</v>
+        <v>83033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R29" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3613,7 +3613,7 @@
         <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,32 +4150,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129643495</v>
+        <v>129643538</v>
       </c>
       <c r="B35" t="n">
-        <v>97020</v>
+        <v>90979</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5685</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>361450</v>
+        <v>361240</v>
       </c>
       <c r="R35" t="n">
-        <v>6599606</v>
+        <v>6599499</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,32 +4257,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129643538</v>
+        <v>129643495</v>
       </c>
       <c r="B36" t="n">
-        <v>90975</v>
+        <v>97024</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>361240</v>
+        <v>361450</v>
       </c>
       <c r="R36" t="n">
-        <v>6599499</v>
+        <v>6599606</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4364,45 +4364,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643548</v>
+        <v>129643524</v>
       </c>
       <c r="B37" t="n">
-        <v>92875</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361330</v>
+        <v>361109</v>
       </c>
       <c r="R37" t="n">
-        <v>6599547</v>
+        <v>6599524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4438,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4448,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4453,6 +4457,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4471,32 +4476,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643494</v>
+        <v>129643548</v>
       </c>
       <c r="B38" t="n">
-        <v>97020</v>
+        <v>92879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4506,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361360</v>
+        <v>361330</v>
       </c>
       <c r="R38" t="n">
-        <v>6599480</v>
+        <v>6599547</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,7 +4546,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,49 +4583,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643524</v>
+        <v>129643494</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>97024</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361109</v>
+        <v>361360</v>
       </c>
       <c r="R39" t="n">
-        <v>6599524</v>
+        <v>6599480</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4652,7 +4653,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4662,7 +4663,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,7 +4672,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,45 +4909,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B42" t="n">
-        <v>97020</v>
+        <v>98778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R42" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4989,7 +4993,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,6 +5002,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5019,7 +5024,7 @@
         <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5123,49 +5128,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>97024</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R44" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,7 +5198,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5207,7 +5208,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,7 +5217,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,45 +5566,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B48" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R48" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,7 +5640,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,6 +5659,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5673,49 +5678,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R49" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5747,7 +5748,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5757,7 +5758,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5767,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R7" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B8" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R8" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627568</v>
+        <v>129627554</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>56926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361409</v>
+        <v>361293</v>
       </c>
       <c r="R12" t="n">
-        <v>6599609</v>
+        <v>6599542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1847,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627554</v>
+        <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>56926</v>
+        <v>98780</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361293</v>
+        <v>361409</v>
       </c>
       <c r="R13" t="n">
-        <v>6599542</v>
+        <v>6599609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627560</v>
+        <v>129627573</v>
       </c>
       <c r="B20" t="n">
-        <v>97060</v>
+        <v>98780</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361478</v>
+        <v>361160</v>
       </c>
       <c r="R20" t="n">
-        <v>6599641</v>
+        <v>6599438</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627573</v>
+        <v>129627560</v>
       </c>
       <c r="B21" t="n">
-        <v>98778</v>
+        <v>97062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361160</v>
+        <v>361478</v>
       </c>
       <c r="R21" t="n">
-        <v>6599438</v>
+        <v>6599641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83042</v>
+        <v>83044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>129643507</v>
       </c>
       <c r="B25" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>129643527</v>
       </c>
       <c r="B27" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>129643519</v>
       </c>
       <c r="B28" t="n">
-        <v>97060</v>
+        <v>97062</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         <v>129643536</v>
       </c>
       <c r="B29" t="n">
-        <v>83033</v>
+        <v>83035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,32 +4150,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129643538</v>
+        <v>129643495</v>
       </c>
       <c r="B35" t="n">
-        <v>90979</v>
+        <v>97026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>361240</v>
+        <v>361450</v>
       </c>
       <c r="R35" t="n">
-        <v>6599499</v>
+        <v>6599606</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,32 +4257,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129643495</v>
+        <v>129643538</v>
       </c>
       <c r="B36" t="n">
-        <v>97024</v>
+        <v>90981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>5685</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>361450</v>
+        <v>361240</v>
       </c>
       <c r="R36" t="n">
-        <v>6599606</v>
+        <v>6599499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4364,49 +4364,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643524</v>
+        <v>129643494</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>97026</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361109</v>
+        <v>361360</v>
       </c>
       <c r="R37" t="n">
-        <v>6599524</v>
+        <v>6599480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4448,7 +4444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4457,7 +4453,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4479,7 +4474,7 @@
         <v>129643548</v>
       </c>
       <c r="B38" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4583,45 +4578,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643494</v>
+        <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>97024</v>
+        <v>98780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361360</v>
+        <v>361109</v>
       </c>
       <c r="R39" t="n">
-        <v>6599480</v>
+        <v>6599524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,7 +4652,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4663,7 +4662,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,6 +4671,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,49 +4690,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R40" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,7 +4760,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4783,7 +4779,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4802,45 +4797,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B41" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R41" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4882,7 +4881,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4891,6 +4890,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,49 +4909,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>98778</v>
+        <v>97026</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R42" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4993,7 +4989,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +4998,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5024,7 +5019,7 @@
         <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5128,45 +5123,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>97024</v>
+        <v>98780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R44" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5197,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5207,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,6 +5216,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,49 +5566,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R48" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5640,7 +5636,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5650,7 +5646,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5655,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5678,45 +5673,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R49" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5747,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5758,7 +5757,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5767,6 +5766,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -4690,45 +4690,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R40" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4764,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,6 +4783,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4797,49 +4802,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R41" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AY58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B28" t="n">
-        <v>97062</v>
+        <v>83035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R28" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B29" t="n">
-        <v>83035</v>
+        <v>97062</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R29" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5566,45 +5566,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B48" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R48" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,7 +5640,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,6 +5659,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5673,49 +5678,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B49" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R49" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5747,7 +5748,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5757,7 +5758,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5767,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6220,6 +6220,568 @@
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129896335</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>361108</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6599525</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>S-Arv-0913</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129896339</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>361161</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6599447</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>S-Arv-0909</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129896341</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>361398</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6599608</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>S-Arv-0907</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>5 dellokaler. 6603554-1315781, 13 ex; 6603577-1315781, 25 ex; 6603578-1315793; 6603588-1315776, 34 ex; 6603601-1315803.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129896343</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>361441</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6599560</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>S-Arv-0905</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129896342</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>361382</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6599667</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>S-Arv-0906</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>129627569</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129627570</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627573</v>
+        <v>129627560</v>
       </c>
       <c r="B20" t="n">
-        <v>98780</v>
+        <v>97072</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361160</v>
+        <v>361478</v>
       </c>
       <c r="R20" t="n">
-        <v>6599438</v>
+        <v>6599641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627560</v>
+        <v>129627573</v>
       </c>
       <c r="B21" t="n">
-        <v>97062</v>
+        <v>98790</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361478</v>
+        <v>361160</v>
       </c>
       <c r="R21" t="n">
-        <v>6599641</v>
+        <v>6599438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3060,10 +3060,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643507</v>
+        <v>129643517</v>
       </c>
       <c r="B25" t="n">
-        <v>91563</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3071,34 +3071,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361447</v>
+        <v>361186</v>
       </c>
       <c r="R25" t="n">
-        <v>6599629</v>
+        <v>6599443</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3130,7 +3139,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3140,7 +3149,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,6 +3158,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3167,54 +3177,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R26" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,7 +3251,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3256,7 +3261,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3284,49 +3289,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643527</v>
+        <v>129643507</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>91563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361330</v>
+        <v>361447</v>
       </c>
       <c r="R27" t="n">
-        <v>6599531</v>
+        <v>6599629</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3359,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3369,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,7 +3378,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>129643519</v>
       </c>
       <c r="B29" t="n">
-        <v>97062</v>
+        <v>97072</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>129643495</v>
       </c>
       <c r="B35" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,45 +4364,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643494</v>
+        <v>129643524</v>
       </c>
       <c r="B37" t="n">
-        <v>97026</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361360</v>
+        <v>361109</v>
       </c>
       <c r="R37" t="n">
-        <v>6599480</v>
+        <v>6599524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4438,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4448,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4453,6 +4457,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4471,32 +4476,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643548</v>
+        <v>129643494</v>
       </c>
       <c r="B38" t="n">
-        <v>92881</v>
+        <v>97036</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4506,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361330</v>
+        <v>361360</v>
       </c>
       <c r="R38" t="n">
-        <v>6599547</v>
+        <v>6599480</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,7 +4546,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4551,7 +4556,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,49 +4583,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643524</v>
+        <v>129643548</v>
       </c>
       <c r="B39" t="n">
-        <v>98780</v>
+        <v>92881</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361109</v>
+        <v>361330</v>
       </c>
       <c r="R39" t="n">
-        <v>6599524</v>
+        <v>6599547</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4652,7 +4653,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4662,7 +4663,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,7 +4672,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,49 +4690,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R40" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,7 +4760,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4783,7 +4779,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4802,45 +4797,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B41" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R41" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4882,7 +4881,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4891,6 +4890,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,45 +4909,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B42" t="n">
-        <v>97026</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R42" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4989,7 +4993,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,6 +5002,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5016,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643497</v>
+        <v>129643501</v>
       </c>
       <c r="B43" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5051,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361373</v>
+        <v>361403</v>
       </c>
       <c r="R43" t="n">
-        <v>6599657</v>
+        <v>6599594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5086,7 +5091,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5123,49 +5128,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643522</v>
+        <v>129643497</v>
       </c>
       <c r="B44" t="n">
-        <v>98780</v>
+        <v>97036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361185</v>
+        <v>361373</v>
       </c>
       <c r="R44" t="n">
-        <v>6599497</v>
+        <v>6599657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,7 +5198,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5207,7 +5208,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,7 +5217,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5345,7 +5345,7 @@
         <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5566,49 +5566,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R48" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5640,7 +5636,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5650,7 +5646,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5655,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5678,45 +5673,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R49" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5747,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5758,7 +5757,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5767,6 +5766,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6269,7 +6269,7 @@
         <v>361108</v>
       </c>
       <c r="R54" t="n">
-        <v>6599525</v>
+        <v>6599524</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B7" t="n">
         <v>98790</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R7" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B8" t="n">
         <v>98790</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R8" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627554</v>
+        <v>129627568</v>
       </c>
       <c r="B12" t="n">
-        <v>56926</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361293</v>
+        <v>361409</v>
       </c>
       <c r="R12" t="n">
-        <v>6599542</v>
+        <v>6599609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,11 +1816,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1847,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627568</v>
+        <v>129627554</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>56926</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1882,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361409</v>
+        <v>361293</v>
       </c>
       <c r="R13" t="n">
-        <v>6599609</v>
+        <v>6599542</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,6 +1913,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B18" t="n">
-        <v>91563</v>
+        <v>57896</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R18" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B19" t="n">
-        <v>57896</v>
+        <v>91563</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R19" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3060,54 +3060,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R25" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,7 +3134,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3149,7 +3144,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3177,49 +3172,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643527</v>
+        <v>129643507</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>91563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361330</v>
+        <v>361447</v>
       </c>
       <c r="R26" t="n">
-        <v>6599531</v>
+        <v>6599629</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3251,7 +3242,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3261,7 +3252,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,7 +3261,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3289,10 +3279,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643507</v>
+        <v>129643517</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,34 +3290,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361447</v>
+        <v>361186</v>
       </c>
       <c r="R27" t="n">
-        <v>6599629</v>
+        <v>6599443</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3359,7 +3358,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3369,7 +3368,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3378,6 +3377,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4909,49 +4909,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R42" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4993,7 +4989,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +4998,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5021,7 +5016,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643501</v>
+        <v>129643497</v>
       </c>
       <c r="B43" t="n">
         <v>97036</v>
@@ -5056,10 +5051,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361403</v>
+        <v>361373</v>
       </c>
       <c r="R43" t="n">
-        <v>6599594</v>
+        <v>6599657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,7 +5086,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5101,7 +5096,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5128,45 +5123,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643497</v>
+        <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>97036</v>
+        <v>98790</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361373</v>
+        <v>361185</v>
       </c>
       <c r="R44" t="n">
-        <v>6599657</v>
+        <v>6599497</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5197,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5207,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,6 +5216,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B7" t="n">
         <v>98790</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R7" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B8" t="n">
         <v>98790</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R8" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627568</v>
+        <v>129627554</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>56926</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361409</v>
+        <v>361293</v>
       </c>
       <c r="R12" t="n">
-        <v>6599609</v>
+        <v>6599542</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1816,6 +1816,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1847,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627554</v>
+        <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>56926</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361293</v>
+        <v>361409</v>
       </c>
       <c r="R13" t="n">
-        <v>6599542</v>
+        <v>6599609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,11 +1918,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>97036</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R30" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R31" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4364,49 +4364,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643524</v>
+        <v>129643494</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361109</v>
+        <v>361360</v>
       </c>
       <c r="R37" t="n">
-        <v>6599524</v>
+        <v>6599480</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4438,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4448,7 +4444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4457,7 +4453,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4476,32 +4471,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643494</v>
+        <v>129643548</v>
       </c>
       <c r="B38" t="n">
-        <v>97036</v>
+        <v>92881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4511,10 +4506,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361360</v>
+        <v>361330</v>
       </c>
       <c r="R38" t="n">
-        <v>6599480</v>
+        <v>6599547</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4546,7 +4541,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4556,7 +4551,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4583,45 +4578,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643548</v>
+        <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>92881</v>
+        <v>98790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361330</v>
+        <v>361109</v>
       </c>
       <c r="R39" t="n">
-        <v>6599547</v>
+        <v>6599524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,7 +4652,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4663,7 +4662,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,6 +4671,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,45 +4690,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R40" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4764,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,6 +4783,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4797,49 +4802,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>98790</v>
+        <v>91599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R41" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,45 +4909,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B42" t="n">
-        <v>97036</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R42" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4989,7 +4993,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,6 +5002,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5016,7 +5021,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643497</v>
+        <v>129643501</v>
       </c>
       <c r="B43" t="n">
         <v>97036</v>
@@ -5051,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361373</v>
+        <v>361403</v>
       </c>
       <c r="R43" t="n">
-        <v>6599657</v>
+        <v>6599594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5086,7 +5091,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5123,49 +5128,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643522</v>
+        <v>129643497</v>
       </c>
       <c r="B44" t="n">
-        <v>98790</v>
+        <v>97036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361185</v>
+        <v>361373</v>
       </c>
       <c r="R44" t="n">
-        <v>6599497</v>
+        <v>6599657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,7 +5198,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5207,7 +5208,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,7 +5217,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5900,7 +5900,7 @@
         <v>129752896</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129752901</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1263,7 +1263,7 @@
         <v>129627569</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>129627570</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129627554</v>
       </c>
       <c r="B12" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>91566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R18" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B19" t="n">
-        <v>91563</v>
+        <v>57895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R19" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,32 +2531,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627560</v>
+        <v>129627573</v>
       </c>
       <c r="B20" t="n">
-        <v>97072</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361478</v>
+        <v>361160</v>
       </c>
       <c r="R20" t="n">
-        <v>6599641</v>
+        <v>6599438</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627573</v>
+        <v>129627560</v>
       </c>
       <c r="B21" t="n">
-        <v>98790</v>
+        <v>97076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361160</v>
+        <v>361478</v>
       </c>
       <c r="R21" t="n">
-        <v>6599438</v>
+        <v>6599641</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83044</v>
+        <v>83047</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,49 +3060,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643527</v>
+        <v>129643517</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>8450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361330</v>
+        <v>361186</v>
       </c>
       <c r="R25" t="n">
-        <v>6599531</v>
+        <v>6599443</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3144,7 +3149,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3172,45 +3177,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643507</v>
+        <v>129643527</v>
       </c>
       <c r="B26" t="n">
-        <v>91563</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361447</v>
+        <v>361330</v>
       </c>
       <c r="R26" t="n">
-        <v>6599629</v>
+        <v>6599531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3242,7 +3251,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3252,7 +3261,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3261,6 +3270,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3279,10 +3289,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643517</v>
+        <v>129643507</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,43 +3300,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361186</v>
+        <v>361447</v>
       </c>
       <c r="R27" t="n">
-        <v>6599443</v>
+        <v>6599629</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3359,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3369,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,7 +3378,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B28" t="n">
-        <v>83035</v>
+        <v>97076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R28" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B29" t="n">
-        <v>97072</v>
+        <v>83038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R29" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3613,7 +3613,7 @@
         <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>129643495</v>
       </c>
       <c r="B35" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>129643538</v>
       </c>
       <c r="B36" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>129643494</v>
       </c>
       <c r="B37" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>129643548</v>
       </c>
       <c r="B38" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4581,7 +4581,7 @@
         <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4909,49 +4909,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>97040</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R42" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4993,7 +4989,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +4998,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5021,10 +5016,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643501</v>
+        <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5056,10 +5051,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361403</v>
+        <v>361373</v>
       </c>
       <c r="R43" t="n">
-        <v>6599594</v>
+        <v>6599657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,7 +5086,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5101,7 +5096,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5128,45 +5123,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643497</v>
+        <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>97036</v>
+        <v>98794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361373</v>
+        <v>361185</v>
       </c>
       <c r="R44" t="n">
-        <v>6599657</v>
+        <v>6599497</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5197,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5207,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,6 +5216,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -3060,54 +3060,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B25" t="n">
-        <v>8450</v>
+        <v>98794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R25" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,7 +3134,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3149,7 +3144,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3177,49 +3172,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643527</v>
+        <v>129643507</v>
       </c>
       <c r="B26" t="n">
-        <v>98794</v>
+        <v>91566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361330</v>
+        <v>361447</v>
       </c>
       <c r="R26" t="n">
-        <v>6599531</v>
+        <v>6599629</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3251,7 +3242,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3261,7 +3252,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,7 +3261,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3289,10 +3279,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643507</v>
+        <v>129643517</v>
       </c>
       <c r="B27" t="n">
-        <v>91566</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,34 +3290,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361447</v>
+        <v>361186</v>
       </c>
       <c r="R27" t="n">
-        <v>6599629</v>
+        <v>6599443</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3359,7 +3358,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3369,7 +3368,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3378,6 +3377,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3824,45 +3824,49 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129643499</v>
+        <v>129643528</v>
       </c>
       <c r="B32" t="n">
-        <v>97040</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361389</v>
+        <v>361397</v>
       </c>
       <c r="R32" t="n">
-        <v>6599624</v>
+        <v>6599608</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3894,7 +3898,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3904,7 +3908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3913,6 +3917,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3931,49 +3936,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129643528</v>
+        <v>129643499</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>97040</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>361397</v>
+        <v>361389</v>
       </c>
       <c r="R33" t="n">
-        <v>6599608</v>
+        <v>6599624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4005,7 +4006,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4015,7 +4016,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,7 +4025,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -5566,45 +5566,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B48" t="n">
-        <v>91602</v>
+        <v>98794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R48" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5636,7 +5640,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,6 +5659,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5673,49 +5678,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B49" t="n">
-        <v>98794</v>
+        <v>91602</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R49" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5747,7 +5748,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5757,7 +5758,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,7 +5767,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B7" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R7" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R8" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1457,7 @@
         <v>129627577</v>
       </c>
       <c r="B9" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>129627548</v>
       </c>
       <c r="B10" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>129627554</v>
       </c>
       <c r="B12" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129627568</v>
       </c>
       <c r="B13" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>129627572</v>
       </c>
       <c r="B14" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129627574</v>
       </c>
       <c r="B15" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>129627567</v>
       </c>
       <c r="B16" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         <v>129627563</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>129627549</v>
       </c>
       <c r="B18" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,7 +2437,7 @@
         <v>129627556</v>
       </c>
       <c r="B19" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2531,32 +2531,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627573</v>
+        <v>129627560</v>
       </c>
       <c r="B20" t="n">
-        <v>98794</v>
+        <v>97079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361160</v>
+        <v>361478</v>
       </c>
       <c r="R20" t="n">
-        <v>6599438</v>
+        <v>6599641</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,32 +2628,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627560</v>
+        <v>129627573</v>
       </c>
       <c r="B21" t="n">
-        <v>97076</v>
+        <v>98797</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361478</v>
+        <v>361160</v>
       </c>
       <c r="R21" t="n">
-        <v>6599641</v>
+        <v>6599438</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>129627571</v>
       </c>
       <c r="B22" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83047</v>
+        <v>83050</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,49 +3060,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643527</v>
+        <v>129643517</v>
       </c>
       <c r="B25" t="n">
-        <v>98794</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361330</v>
+        <v>361186</v>
       </c>
       <c r="R25" t="n">
-        <v>6599531</v>
+        <v>6599443</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3144,7 +3149,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3175,7 +3180,7 @@
         <v>129643507</v>
       </c>
       <c r="B26" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,54 +3284,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R27" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B28" t="n">
-        <v>97076</v>
+        <v>83041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R28" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B29" t="n">
-        <v>83038</v>
+        <v>97079</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R29" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3613,7 +3613,7 @@
         <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643528</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>129643499</v>
       </c>
       <c r="B33" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4150,32 +4150,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129643495</v>
+        <v>129643538</v>
       </c>
       <c r="B35" t="n">
-        <v>97040</v>
+        <v>90987</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>5685</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>361450</v>
+        <v>361240</v>
       </c>
       <c r="R35" t="n">
-        <v>6599606</v>
+        <v>6599499</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4257,32 +4257,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129643538</v>
+        <v>129643495</v>
       </c>
       <c r="B36" t="n">
-        <v>90984</v>
+        <v>97043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5685</v>
+        <v>53</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4292,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>361240</v>
+        <v>361450</v>
       </c>
       <c r="R36" t="n">
-        <v>6599499</v>
+        <v>6599606</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4367,7 +4367,7 @@
         <v>129643494</v>
       </c>
       <c r="B37" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4471,45 +4471,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643548</v>
+        <v>129643524</v>
       </c>
       <c r="B38" t="n">
-        <v>92884</v>
+        <v>98797</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361330</v>
+        <v>361109</v>
       </c>
       <c r="R38" t="n">
-        <v>6599547</v>
+        <v>6599524</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,7 +4545,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4551,7 +4555,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4560,6 +4564,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4578,49 +4583,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643524</v>
+        <v>129643548</v>
       </c>
       <c r="B39" t="n">
-        <v>98794</v>
+        <v>92887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361109</v>
+        <v>361330</v>
       </c>
       <c r="R39" t="n">
-        <v>6599524</v>
+        <v>6599547</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4652,7 +4653,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4662,7 +4663,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4671,7 +4672,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,49 +4690,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B40" t="n">
-        <v>98794</v>
+        <v>91605</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R40" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4764,7 +4760,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4774,7 +4770,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4783,7 +4779,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4802,45 +4797,49 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B41" t="n">
-        <v>91602</v>
+        <v>98797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R41" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4872,7 +4871,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4882,7 +4881,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4891,6 +4890,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5019,7 +5019,7 @@
         <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129643531</v>
+        <v>129643521</v>
       </c>
       <c r="B46" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>361166</v>
+        <v>361383</v>
       </c>
       <c r="R46" t="n">
-        <v>6599518</v>
+        <v>6599668</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5454,10 +5454,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129643521</v>
+        <v>129643531</v>
       </c>
       <c r="B47" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>361383</v>
+        <v>361166</v>
       </c>
       <c r="R47" t="n">
-        <v>6599668</v>
+        <v>6599518</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5569,7 +5569,7 @@
         <v>129643530</v>
       </c>
       <c r="B48" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>129643513</v>
       </c>
       <c r="B49" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>129752896</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6013,7 +6013,7 @@
         <v>129752901</v>
       </c>
       <c r="B52" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B7" t="n">
         <v>98797</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R7" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B8" t="n">
         <v>98797</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R8" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2337,32 +2337,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627549</v>
+        <v>129627556</v>
       </c>
       <c r="B18" t="n">
-        <v>91569</v>
+        <v>57898</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361126</v>
+        <v>361119</v>
       </c>
       <c r="R18" t="n">
-        <v>6599478</v>
+        <v>6599499</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,32 +2434,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627556</v>
+        <v>129627549</v>
       </c>
       <c r="B19" t="n">
-        <v>57898</v>
+        <v>91569</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361119</v>
+        <v>361126</v>
       </c>
       <c r="R19" t="n">
-        <v>6599499</v>
+        <v>6599478</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B30" t="n">
-        <v>98797</v>
+        <v>97043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R30" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B31" t="n">
-        <v>97043</v>
+        <v>98797</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R31" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -1260,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627569</v>
+        <v>129627570</v>
       </c>
       <c r="B7" t="n">
         <v>98797</v>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361314</v>
+        <v>361245</v>
       </c>
       <c r="R7" t="n">
-        <v>6599556</v>
+        <v>6599497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627570</v>
+        <v>129627569</v>
       </c>
       <c r="B8" t="n">
         <v>98797</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361245</v>
+        <v>361314</v>
       </c>
       <c r="R8" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3610,32 +3610,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643503</v>
+        <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>97043</v>
+        <v>98797</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361226</v>
+        <v>361441</v>
       </c>
       <c r="R30" t="n">
-        <v>6599503</v>
+        <v>6599559</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643535</v>
+        <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>98797</v>
+        <v>97043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361441</v>
+        <v>361226</v>
       </c>
       <c r="R31" t="n">
-        <v>6599559</v>
+        <v>6599503</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3824,49 +3824,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129643528</v>
+        <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>97043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361397</v>
+        <v>361389</v>
       </c>
       <c r="R32" t="n">
-        <v>6599608</v>
+        <v>6599624</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3898,7 +3894,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3908,7 +3904,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3917,7 +3913,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3936,45 +3931,49 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129643499</v>
+        <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>97043</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>361389</v>
+        <v>361397</v>
       </c>
       <c r="R33" t="n">
-        <v>6599624</v>
+        <v>6599608</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4006,7 +4005,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4016,7 +4015,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4025,6 +4024,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4909,45 +4909,49 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643501</v>
+        <v>129643522</v>
       </c>
       <c r="B42" t="n">
-        <v>97043</v>
+        <v>98797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361403</v>
+        <v>361185</v>
       </c>
       <c r="R42" t="n">
-        <v>6599594</v>
+        <v>6599497</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4979,7 +4983,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4989,7 +4993,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4998,6 +5002,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5016,7 +5021,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643497</v>
+        <v>129643501</v>
       </c>
       <c r="B43" t="n">
         <v>97043</v>
@@ -5051,10 +5056,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361373</v>
+        <v>361403</v>
       </c>
       <c r="R43" t="n">
-        <v>6599657</v>
+        <v>6599594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5086,7 +5091,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5096,7 +5101,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5123,49 +5128,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643522</v>
+        <v>129643497</v>
       </c>
       <c r="B44" t="n">
-        <v>98797</v>
+        <v>97043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361185</v>
+        <v>361373</v>
       </c>
       <c r="R44" t="n">
-        <v>6599497</v>
+        <v>6599657</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5197,7 +5198,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5207,7 +5208,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,7 +5217,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -2825,7 +2825,7 @@
         <v>129643553</v>
       </c>
       <c r="B23" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>129643550</v>
       </c>
       <c r="B24" t="n">
-        <v>83050</v>
+        <v>83051</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3060,54 +3060,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643517</v>
+        <v>129643527</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>98798</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361186</v>
+        <v>361330</v>
       </c>
       <c r="R25" t="n">
-        <v>6599443</v>
+        <v>6599531</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3139,7 +3134,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3149,7 +3144,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3180,7 +3175,7 @@
         <v>129643507</v>
       </c>
       <c r="B26" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3284,49 +3279,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643527</v>
+        <v>129643517</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361330</v>
+        <v>361186</v>
       </c>
       <c r="R27" t="n">
-        <v>6599531</v>
+        <v>6599443</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643536</v>
+        <v>129643519</v>
       </c>
       <c r="B28" t="n">
-        <v>83041</v>
+        <v>97080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>2590</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361219</v>
+        <v>361402</v>
       </c>
       <c r="R28" t="n">
-        <v>6599399</v>
+        <v>6599574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B29" t="n">
-        <v>97079</v>
+        <v>83042</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,21 +3514,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3538,10 +3538,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R29" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3573,7 +3573,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3613,7 +3613,7 @@
         <v>129643535</v>
       </c>
       <c r="B30" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>129643503</v>
       </c>
       <c r="B31" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>129643499</v>
       </c>
       <c r="B32" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>129643528</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>129643545</v>
       </c>
       <c r="B34" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>129643538</v>
       </c>
       <c r="B35" t="n">
-        <v>90987</v>
+        <v>90988</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>129643495</v>
       </c>
       <c r="B36" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4364,32 +4364,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643494</v>
+        <v>129643548</v>
       </c>
       <c r="B37" t="n">
-        <v>97043</v>
+        <v>92888</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4399,10 +4399,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361360</v>
+        <v>361330</v>
       </c>
       <c r="R37" t="n">
-        <v>6599480</v>
+        <v>6599547</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4471,49 +4471,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643524</v>
+        <v>129643494</v>
       </c>
       <c r="B38" t="n">
-        <v>98797</v>
+        <v>97044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361109</v>
+        <v>361360</v>
       </c>
       <c r="R38" t="n">
-        <v>6599524</v>
+        <v>6599480</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4545,7 +4541,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4555,7 +4551,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4564,7 +4560,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4583,45 +4578,49 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643548</v>
+        <v>129643524</v>
       </c>
       <c r="B39" t="n">
-        <v>92887</v>
+        <v>98798</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361330</v>
+        <v>361109</v>
       </c>
       <c r="R39" t="n">
-        <v>6599547</v>
+        <v>6599524</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4653,7 +4652,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4663,7 +4662,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4672,6 +4671,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4690,45 +4690,49 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643511</v>
+        <v>129643525</v>
       </c>
       <c r="B40" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361337</v>
+        <v>361392</v>
       </c>
       <c r="R40" t="n">
-        <v>6599454</v>
+        <v>6599618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4760,7 +4764,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4770,7 +4774,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,6 +4783,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4797,49 +4802,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643525</v>
+        <v>129643511</v>
       </c>
       <c r="B41" t="n">
-        <v>98797</v>
+        <v>91606</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361392</v>
+        <v>361337</v>
       </c>
       <c r="R41" t="n">
-        <v>6599618</v>
+        <v>6599454</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4871,7 +4872,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4881,7 +4882,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4890,7 +4891,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4909,49 +4909,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643522</v>
+        <v>129643501</v>
       </c>
       <c r="B42" t="n">
-        <v>98797</v>
+        <v>97044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361185</v>
+        <v>361403</v>
       </c>
       <c r="R42" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4983,7 +4979,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4993,7 +4989,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5002,7 +4998,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5021,10 +5016,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643501</v>
+        <v>129643497</v>
       </c>
       <c r="B43" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5056,10 +5051,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361403</v>
+        <v>361373</v>
       </c>
       <c r="R43" t="n">
-        <v>6599594</v>
+        <v>6599657</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5091,7 +5086,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5101,7 +5096,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5128,45 +5123,49 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643497</v>
+        <v>129643522</v>
       </c>
       <c r="B44" t="n">
-        <v>97043</v>
+        <v>98798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361373</v>
+        <v>361185</v>
       </c>
       <c r="R44" t="n">
-        <v>6599657</v>
+        <v>6599497</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5198,7 +5197,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5208,7 +5207,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5217,6 +5216,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5238,7 +5238,7 @@
         <v>129643509</v>
       </c>
       <c r="B45" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5342,10 +5342,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129643521</v>
+        <v>129643531</v>
       </c>
       <c r="B46" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>361383</v>
+        <v>361166</v>
       </c>
       <c r="R46" t="n">
-        <v>6599668</v>
+        <v>6599518</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5454,10 +5454,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129643531</v>
+        <v>129643521</v>
       </c>
       <c r="B47" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>361166</v>
+        <v>361383</v>
       </c>
       <c r="R47" t="n">
-        <v>6599518</v>
+        <v>6599668</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5566,49 +5566,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643530</v>
+        <v>129643513</v>
       </c>
       <c r="B48" t="n">
-        <v>98797</v>
+        <v>91606</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361241</v>
+        <v>361108</v>
       </c>
       <c r="R48" t="n">
-        <v>6599344</v>
+        <v>6599524</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5640,7 +5636,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5650,7 +5646,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5659,7 +5655,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5678,45 +5673,49 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643513</v>
+        <v>129643530</v>
       </c>
       <c r="B49" t="n">
-        <v>91605</v>
+        <v>98798</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361108</v>
+        <v>361241</v>
       </c>
       <c r="R49" t="n">
-        <v>6599524</v>
+        <v>6599344</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,7 +5747,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5758,7 +5757,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5767,6 +5766,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5788,7 +5788,7 @@
         <v>129643533</v>
       </c>
       <c r="B50" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -6003,7 +6003,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Carlzon, Torbjörn Westerberg</t>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Carlzon, Torbjörn Westerberg</t>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6123,7 +6123,7 @@
         <v>129752902</v>
       </c>
       <c r="B53" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Carlzon, Torbjörn Westerberg</t>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -6225,7 +6225,7 @@
         <v>129896335</v>
       </c>
       <c r="B54" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>129896339</v>
       </c>
       <c r="B55" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>129896341</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>129896343</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>129896342</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 53871-2025 artfynd.xlsx
+++ b/artfynd/A 53871-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84244327</v>
+        <v>129627548</v>
       </c>
       <c r="B2" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lyserudsåsen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361149.8911520253</v>
+        <v>361471</v>
       </c>
       <c r="R2" t="n">
-        <v>6599281.220896384</v>
+        <v>6599632</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>84244335</v>
+        <v>129643494</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lyserudsåsen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>361010.9849389662</v>
+        <v>361360</v>
       </c>
       <c r="R3" t="n">
-        <v>6599461.11837408</v>
+        <v>6599480</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +837,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,69 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98052071</v>
+        <v>129643495</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>360999.5228702108</v>
+        <v>361450</v>
       </c>
       <c r="R4" t="n">
-        <v>6599453.921583855</v>
+        <v>6599606</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,22 +944,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,83 +968,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Rees, Per Gustafsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98052082</v>
+        <v>129643497</v>
       </c>
       <c r="B5" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>360999.5228702108</v>
+        <v>361373</v>
       </c>
       <c r="R5" t="n">
-        <v>6599453.921583855</v>
+        <v>6599657</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,34 +1075,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Rees, Per Gustafsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98052068</v>
+        <v>129643499</v>
       </c>
       <c r="B6" t="n">
-        <v>56401</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,45 +1104,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100048</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>360901.2848806324</v>
+        <v>361389</v>
       </c>
       <c r="R6" t="n">
-        <v>6599302.093276414</v>
+        <v>6599624</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,22 +1158,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,57 +1188,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Rees, Per Gustafsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129627570</v>
+        <v>129643501</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361245</v>
+        <v>361403</v>
       </c>
       <c r="R7" t="n">
-        <v>6599497</v>
+        <v>6599594</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,9 +1268,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,57 +1295,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129627569</v>
+        <v>129643503</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361314</v>
+        <v>361226</v>
       </c>
       <c r="R8" t="n">
-        <v>6599556</v>
+        <v>6599503</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,9 +1375,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,57 +1402,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129627577</v>
+        <v>129643550</v>
       </c>
       <c r="B9" t="n">
-        <v>92887</v>
+        <v>83299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361250</v>
+        <v>361219</v>
       </c>
       <c r="R9" t="n">
-        <v>6599499</v>
+        <v>6599399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,39 +1485,70 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # högstubbe av björk # Betula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129627548</v>
+        <v>129627550</v>
       </c>
       <c r="B10" t="n">
-        <v>97043</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,21 +1556,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>361471</v>
+        <v>361385</v>
       </c>
       <c r="R10" t="n">
-        <v>6599632</v>
+        <v>6599453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,7 +1645,7 @@
         <v>129627552</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,45 +1739,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129627554</v>
+        <v>129643511</v>
       </c>
       <c r="B12" t="n">
-        <v>56930</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>361293</v>
+        <v>361337</v>
       </c>
       <c r="R12" t="n">
-        <v>6599542</v>
+        <v>6599454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1813,14 +1807,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,57 +1834,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129627568</v>
+        <v>129643513</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>361409</v>
+        <v>361108</v>
       </c>
       <c r="R13" t="n">
-        <v>6599609</v>
+        <v>6599524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,9 +1914,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1932,44 +1941,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129627572</v>
+        <v>129627560</v>
       </c>
       <c r="B14" t="n">
-        <v>98797</v>
+        <v>97394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1988,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>361114</v>
+        <v>361478</v>
       </c>
       <c r="R14" t="n">
-        <v>6599489</v>
+        <v>6599641</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,45 +2050,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129627574</v>
+        <v>129643519</v>
       </c>
       <c r="B15" t="n">
-        <v>98797</v>
+        <v>97394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>2590</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>361162</v>
+        <v>361402</v>
       </c>
       <c r="R15" t="n">
-        <v>6599456</v>
+        <v>6599574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,9 +2118,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2126,57 +2145,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129627567</v>
+        <v>84244327</v>
       </c>
       <c r="B16" t="n">
-        <v>98797</v>
+        <v>96348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Lyserudsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>361419</v>
+        <v>361150</v>
       </c>
       <c r="R16" t="n">
-        <v>6599632</v>
+        <v>6599281</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,12 +2222,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2223,44 +2242,44 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129627563</v>
+        <v>129627577</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2270,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>361397</v>
+        <v>361250</v>
       </c>
       <c r="R17" t="n">
-        <v>6599585</v>
+        <v>6599499</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,11 +2325,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>13st</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2351,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129627556</v>
+        <v>129627578</v>
       </c>
       <c r="B18" t="n">
-        <v>57898</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2348,21 +2362,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2386,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361119</v>
+        <v>361279</v>
       </c>
       <c r="R18" t="n">
-        <v>6599499</v>
+        <v>6599333</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,45 +2448,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129627549</v>
+        <v>129643545</v>
       </c>
       <c r="B19" t="n">
-        <v>91569</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361126</v>
+        <v>361463</v>
       </c>
       <c r="R19" t="n">
-        <v>6599478</v>
+        <v>6599651</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,9 +2516,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2519,57 +2543,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129627560</v>
+        <v>129643548</v>
       </c>
       <c r="B20" t="n">
-        <v>97079</v>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>361478</v>
+        <v>361330</v>
       </c>
       <c r="R20" t="n">
-        <v>6599641</v>
+        <v>6599547</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2599,9 +2623,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2616,44 +2650,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129627573</v>
+        <v>129627549</v>
       </c>
       <c r="B21" t="n">
-        <v>98797</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2663,10 +2697,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361160</v>
+        <v>361126</v>
       </c>
       <c r="R21" t="n">
-        <v>6599438</v>
+        <v>6599478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2725,45 +2759,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129627571</v>
+        <v>129643507</v>
       </c>
       <c r="B22" t="n">
-        <v>98797</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sovtjärnen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>361155</v>
+        <v>361447</v>
       </c>
       <c r="R22" t="n">
-        <v>6599526</v>
+        <v>6599629</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2793,9 +2827,19 @@
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2810,22 +2854,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129643553</v>
+        <v>129643509</v>
       </c>
       <c r="B23" t="n">
-        <v>92259</v>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2877,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6031</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2901,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>361128</v>
+        <v>361362</v>
       </c>
       <c r="R23" t="n">
-        <v>6599471</v>
+        <v>6599658</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,7 +2936,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2902,7 +2946,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2929,48 +2973,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129643550</v>
+        <v>129643538</v>
       </c>
       <c r="B24" t="n">
-        <v>83051</v>
+        <v>91282</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>308</v>
+        <v>5685</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>361219</v>
+        <v>361240</v>
       </c>
       <c r="R24" t="n">
-        <v>6599399</v>
+        <v>6599499</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,7 +3043,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3012,7 +3053,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3021,29 +3062,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # högstubbe av björk # Betula</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3060,52 +3080,59 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129643527</v>
+        <v>98052082</v>
       </c>
       <c r="B25" t="n">
-        <v>98798</v>
+        <v>92567</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>361330</v>
+        <v>361000</v>
       </c>
       <c r="R25" t="n">
-        <v>6599531</v>
+        <v>6599454</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3129,22 +3156,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:24</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3160,22 +3177,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129643507</v>
+        <v>98052083</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>92567</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,37 +3200,48 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>361447</v>
+        <v>361530</v>
       </c>
       <c r="R26" t="n">
-        <v>6599629</v>
+        <v>6599665</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3237,22 +3265,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3261,28 +3279,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129643517</v>
+        <v>129643553</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>92567</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3290,43 +3309,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6031</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>361186</v>
+        <v>361128</v>
       </c>
       <c r="R27" t="n">
-        <v>6599443</v>
+        <v>6599471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3358,7 +3368,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3368,7 +3378,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,7 +3387,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3396,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129643519</v>
+        <v>129643536</v>
       </c>
       <c r="B28" t="n">
-        <v>97080</v>
+        <v>83290</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3407,21 +3416,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2590</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3431,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>361402</v>
+        <v>361219</v>
       </c>
       <c r="R28" t="n">
-        <v>6599574</v>
+        <v>6599399</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3466,7 +3475,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3476,7 +3485,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3503,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129643536</v>
+        <v>84244350</v>
       </c>
       <c r="B29" t="n">
-        <v>83042</v>
+        <v>80461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3514,34 +3523,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Lyserudsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>361219</v>
+        <v>361373</v>
       </c>
       <c r="R29" t="n">
-        <v>6599399</v>
+        <v>6599461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3568,22 +3577,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3598,60 +3597,68 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129643535</v>
+        <v>98052068</v>
       </c>
       <c r="B30" t="n">
-        <v>98798</v>
+        <v>57966</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100048</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>361441</v>
+        <v>360902</v>
       </c>
       <c r="R30" t="n">
-        <v>6599559</v>
+        <v>6599302</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3675,22 +3682,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3705,57 +3702,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129643503</v>
+        <v>129627557</v>
       </c>
       <c r="B31" t="n">
-        <v>97044</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>361226</v>
+        <v>361370</v>
       </c>
       <c r="R31" t="n">
-        <v>6599503</v>
+        <v>6599434</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3785,19 +3782,14 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:14</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>färska hackmärken</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3812,60 +3804,68 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129643499</v>
+        <v>129752901</v>
       </c>
       <c r="B32" t="n">
-        <v>97044</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Bråne Glaskogen, Vrm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>361389</v>
+        <v>361227</v>
       </c>
       <c r="R32" t="n">
-        <v>6599624</v>
+        <v>6599452</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3889,22 +3889,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Grova hack- och fläkmärken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3919,64 +3914,76 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129643528</v>
+        <v>129752896</v>
       </c>
       <c r="B33" t="n">
-        <v>98798</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Bråne Glaskogen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>361397</v>
+        <v>361227</v>
       </c>
       <c r="R33" t="n">
-        <v>6599608</v>
+        <v>6599452</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4000,22 +4007,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:31</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4024,29 +4021,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Torbjörn Westerberg</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129643545</v>
+        <v>84244347</v>
       </c>
       <c r="B34" t="n">
-        <v>92888</v>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4054,34 +4050,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Lyserudsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>361463</v>
+        <v>361161</v>
       </c>
       <c r="R34" t="n">
-        <v>6599651</v>
+        <v>6599338</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4108,22 +4113,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4138,22 +4133,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129643538</v>
+        <v>129627554</v>
       </c>
       <c r="B35" t="n">
-        <v>90988</v>
+        <v>57141</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4161,34 +4156,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5685</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>361240</v>
+        <v>361293</v>
       </c>
       <c r="R35" t="n">
-        <v>6599499</v>
+        <v>6599542</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4218,19 +4213,14 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:17</t>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4245,22 +4235,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129643495</v>
+        <v>129627556</v>
       </c>
       <c r="B36" t="n">
-        <v>97044</v>
+        <v>58114</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4268,34 +4258,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>361450</v>
+        <v>361119</v>
       </c>
       <c r="R36" t="n">
-        <v>6599606</v>
+        <v>6599499</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4325,19 +4315,9 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4352,22 +4332,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129643548</v>
+        <v>129643517</v>
       </c>
       <c r="B37" t="n">
-        <v>92888</v>
+        <v>8455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4375,34 +4355,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>361330</v>
+        <v>361186</v>
       </c>
       <c r="R37" t="n">
-        <v>6599547</v>
+        <v>6599443</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4434,7 +4423,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4444,7 +4433,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4453,6 +4442,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4471,45 +4461,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129643494</v>
+        <v>84244335</v>
       </c>
       <c r="B38" t="n">
-        <v>97044</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Lyserudsåsen, Vrm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>361360</v>
+        <v>361011</v>
       </c>
       <c r="R38" t="n">
-        <v>6599480</v>
+        <v>6599461</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4536,22 +4526,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:52</t>
+          <t>2020-03-19</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4566,22 +4546,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129643524</v>
+        <v>98052071</v>
       </c>
       <c r="B39" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4606,24 +4586,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>361109</v>
+        <v>361000</v>
       </c>
       <c r="R39" t="n">
-        <v>6599524</v>
+        <v>6599454</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4647,22 +4627,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:01</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4678,22 +4648,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jan Rees, Per Gustafsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129643525</v>
+        <v>129627563</v>
       </c>
       <c r="B40" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4718,21 +4688,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>361392</v>
+        <v>361397</v>
       </c>
       <c r="R40" t="n">
-        <v>6599618</v>
+        <v>6599585</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4762,19 +4728,14 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:31</t>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>13st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4783,64 +4744,63 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129643511</v>
+        <v>129627565</v>
       </c>
       <c r="B41" t="n">
-        <v>91606</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>361337</v>
+        <v>361385</v>
       </c>
       <c r="R41" t="n">
-        <v>6599454</v>
+        <v>6599441</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4870,19 +4830,9 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:56</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:56</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4897,57 +4847,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129643501</v>
+        <v>129627567</v>
       </c>
       <c r="B42" t="n">
-        <v>97044</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>361403</v>
+        <v>361419</v>
       </c>
       <c r="R42" t="n">
-        <v>6599594</v>
+        <v>6599632</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4977,19 +4927,9 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5004,57 +4944,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129643497</v>
+        <v>129627568</v>
       </c>
       <c r="B43" t="n">
-        <v>97044</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>361373</v>
+        <v>361409</v>
       </c>
       <c r="R43" t="n">
-        <v>6599657</v>
+        <v>6599609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,19 +5024,9 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:36</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5111,22 +5041,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129643522</v>
+        <v>129627569</v>
       </c>
       <c r="B44" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5151,21 +5081,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>361185</v>
+        <v>361314</v>
       </c>
       <c r="R44" t="n">
-        <v>6599497</v>
+        <v>6599556</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5195,85 +5121,74 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129643509</v>
+        <v>129627570</v>
       </c>
       <c r="B45" t="n">
-        <v>91570</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>361362</v>
+        <v>361245</v>
       </c>
       <c r="R45" t="n">
-        <v>6599658</v>
+        <v>6599497</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5303,19 +5218,9 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5330,22 +5235,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129643531</v>
+        <v>129627571</v>
       </c>
       <c r="B46" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5370,21 +5275,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>361166</v>
+        <v>361155</v>
       </c>
       <c r="R46" t="n">
-        <v>6599518</v>
+        <v>6599526</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5414,50 +5315,39 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129643521</v>
+        <v>129627572</v>
       </c>
       <c r="B47" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5482,21 +5372,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>361383</v>
+        <v>361114</v>
       </c>
       <c r="R47" t="n">
-        <v>6599668</v>
+        <v>6599489</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5526,85 +5412,74 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:38</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129643513</v>
+        <v>129627573</v>
       </c>
       <c r="B48" t="n">
-        <v>91606</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>361108</v>
+        <v>361160</v>
       </c>
       <c r="R48" t="n">
-        <v>6599524</v>
+        <v>6599438</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5634,19 +5509,9 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5661,22 +5526,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129643530</v>
+        <v>129627574</v>
       </c>
       <c r="B49" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5701,21 +5566,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sydväst Sovtjärnen, Vrm</t>
+          <t>Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>361241</v>
+        <v>361162</v>
       </c>
       <c r="R49" t="n">
-        <v>6599344</v>
+        <v>6599456</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5745,50 +5606,39 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129643533</v>
+        <v>129643521</v>
       </c>
       <c r="B50" t="n">
-        <v>98798</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5815,7 +5665,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>75</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5824,10 +5674,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>361227</v>
+        <v>361383</v>
       </c>
       <c r="R50" t="n">
-        <v>6599494</v>
+        <v>6599668</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5859,7 +5709,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5869,7 +5719,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5897,64 +5747,52 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129752896</v>
+        <v>129643522</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>64</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bråne Glaskogen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>361227</v>
+        <v>361185</v>
       </c>
       <c r="R51" t="n">
-        <v>6599452</v>
+        <v>6599497</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5978,12 +5816,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5992,74 +5840,71 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Torbjörn Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Carlzon, Torbjörn Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129752901</v>
+        <v>129643524</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bråne Glaskogen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>361227</v>
+        <v>361109</v>
       </c>
       <c r="R52" t="n">
-        <v>6599452</v>
+        <v>6599524</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6083,17 +5928,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Grova hack- och fläkmärken</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6102,28 +5952,29 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Torbjörn Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Carlzon, Torbjörn Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129752902</v>
+        <v>129643525</v>
       </c>
       <c r="B53" t="n">
-        <v>98830</v>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6148,24 +5999,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bråne Glaskogen, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>361227</v>
+        <v>361392</v>
       </c>
       <c r="R53" t="n">
-        <v>6599452</v>
+        <v>6599618</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6189,12 +6040,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6210,22 +6071,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Torbjörn Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Carlzon, Torbjörn Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129896335</v>
+        <v>129643527</v>
       </c>
       <c r="B54" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6252,24 +6113,19 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sovtjärnen, SV om, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>361108</v>
+        <v>361330</v>
       </c>
       <c r="R54" t="n">
-        <v>6599524</v>
+        <v>6599531</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6294,34 +6150,40 @@
           <t>Glava</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>S-Arv-0913</t>
-        </is>
-      </c>
       <c r="Y54" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
@@ -6329,18 +6191,14 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129896339</v>
+        <v>129643528</v>
       </c>
       <c r="B55" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6365,17 +6223,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sovtjärnen, SV om, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>361161</v>
+        <v>361397</v>
       </c>
       <c r="R55" t="n">
-        <v>6599447</v>
+        <v>6599608</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6400,53 +6262,55 @@
           <t>Glava</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>S-Arv-0909</t>
-        </is>
-      </c>
       <c r="Y55" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129896341</v>
+        <v>129643530</v>
       </c>
       <c r="B56" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6473,24 +6337,19 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sovtjärnen, S om, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>361398</v>
+        <v>361241</v>
       </c>
       <c r="R56" t="n">
-        <v>6599608</v>
+        <v>6599344</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6515,24 +6374,24 @@
           <t>Glava</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>S-Arv-0907</t>
-        </is>
-      </c>
       <c r="Y56" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>5 dellokaler. 6603554-1315781, 13 ex; 6603577-1315781, 25 ex; 6603578-1315793; 6603588-1315776, 34 ex; 6603601-1315803.</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6541,13 +6400,14 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
@@ -6555,18 +6415,14 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129896343</v>
+        <v>129643531</v>
       </c>
       <c r="B57" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6591,17 +6447,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sovtjärnen, S om, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>361441</v>
+        <v>361166</v>
       </c>
       <c r="R57" t="n">
-        <v>6599560</v>
+        <v>6599518</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6626,34 +6486,40 @@
           <t>Glava</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>S-Arv-0905</t>
-        </is>
-      </c>
       <c r="Y57" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
@@ -6661,18 +6527,14 @@
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129896342</v>
+        <v>129643533</v>
       </c>
       <c r="B58" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6699,24 +6561,19 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>109</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sovtjärnen, S om, Vrm</t>
+          <t>Sydväst Sovtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>361382</v>
+        <v>361227</v>
       </c>
       <c r="R58" t="n">
-        <v>6599667</v>
+        <v>6599494</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6741,42 +6598,921 @@
           <t>Glava</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>S-Arv-0906</t>
-        </is>
-      </c>
       <c r="Y58" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-11-09</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129643535</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Sydväst Sovtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>361441</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6599559</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129752902</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Bråne Glaskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>361227</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6599452</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Torbjörn Westerberg, Göran Carlzon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129896335</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>361108</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6599524</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>S-Arv-0913</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
           <t>Owe Nilsson</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
+      <c r="AX61" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr">
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129896339</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, SV om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>361161</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6599447</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>S-Arv-0909</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129896341</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>361398</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6599608</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>S-Arv-0907</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>5 dellokaler. 6603554-1315781, 13 ex; 6603577-1315781, 25 ex; 6603578-1315793; 6603588-1315776, 34 ex; 6603601-1315803.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129896342</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>361382</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6599667</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>S-Arv-0906</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129896343</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>361441</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6599560</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>S-Arv-0905</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129896344</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Sovtjärnen, S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>361384</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6599441</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Glava</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>S-Arv-0904</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>
